--- a/output/pdf_financials_xlsx/XL.xlsx
+++ b/output/pdf_financials_xlsx/XL.xlsx
@@ -5416,43 +5416,43 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.124443</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.229017</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.152028</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.657588</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>1.645776</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>1.484739</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>1.041196</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>1.653431</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>1.236875</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>1.04681</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>1.017245</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>1.43187</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>2.475143</v>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
@@ -9056,7 +9056,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.124443</v>
       </c>
@@ -12670,7 +12674,11 @@
           <t>Translation reserve 1,711,100</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XL.xlsx
+++ b/output/pdf_financials_xlsx/XL.xlsx
@@ -2463,43 +2463,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.661554</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.481167</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07819</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.140896</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.063903</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.063958</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.086076</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.564057</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.841966</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.328926</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.650008</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.541189</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.443477</v>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
@@ -2565,43 +2565,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.661554</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.481167</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07819</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.140896</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.063903</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.063958</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.086076</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.564057</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.841966</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.328926</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.650008</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.541189</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.443477</v>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
@@ -3177,43 +3177,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.662494</v>
+        <v>0.00094</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.482128</v>
+        <v>0.000961</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07908900000000001</v>
+        <v>0.000899</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.14172</v>
+        <v>0.000824</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.064594</v>
+        <v>0.000691</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06467000000000001</v>
+        <v>0.000712</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.086838</v>
+        <v>0.000762</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.564758</v>
+        <v>0.000701</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.842702</v>
+        <v>0.000736</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.329678</v>
+        <v>0.000752</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.650762</v>
+        <v>0.000754</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.541912</v>
+        <v>0.000723</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.059004</v>
+        <v>0.615527</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -32344,11 +32344,7 @@
           <t>General and administrative fees 14</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -34204,11 +34200,7 @@
           <t>General and administrative fees 15</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -35492,11 +35484,7 @@
           <t>General and administrative fees 13</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XL.xlsx
+++ b/output/pdf_financials_xlsx/XL.xlsx
@@ -1363,7 +1363,7 @@
         <v>-1.60509</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.579556</v>
+        <v>-1.536943</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.042613</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>-1.60509</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.579556</v>
+        <v>-1.536943</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>-1.597714</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.573186</v>
+        <v>-1.530573</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.77258167674403</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -2654,10 +2654,8 @@
       <c r="N37" s="3" t="n">
         <v>0.775403</v>
       </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>0.256734</v>
       </c>
     </row>
     <row r="38">
@@ -6325,19 +6323,19 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.012608</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.100393</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.007837</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.006187</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.002944</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -27052,7 +27050,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -27472,7 +27474,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -35996,7 +36002,11 @@
           <t>Income tax recovery 14</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
